--- a/data/4-reports/3_Proposed_Changes.xlsx
+++ b/data/4-reports/3_Proposed_Changes.xlsx
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001115</t>
+          <t>ARI:0001113</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001115</t>
+          <t>ARI:0001113</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001115</t>
+          <t>ARI:0001113</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001144</t>
+          <t>ARI:0001141</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001144</t>
+          <t>ARI:0001141</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001154</t>
+          <t>ARI:0001151</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">

--- a/data/4-reports/3_Proposed_Changes.xlsx
+++ b/data/4-reports/3_Proposed_Changes.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>ARI:0001034</t>
+          <t>ARI:0001033</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ARI:0001035</t>
+          <t>ARI:0001034</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -700,7 +700,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ARI:0001035</t>
+          <t>ARI:0001034</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ARI:0001045</t>
+          <t>ARI:0001044</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>ARI:0001058</t>
+          <t>ARI:0001057</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ARI:0001070</t>
+          <t>ARI:0001069</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001113</t>
+          <t>ARI:0001112</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001113</t>
+          <t>ARI:0001112</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001113</t>
+          <t>ARI:0001112</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001141</t>
+          <t>ARI:0001140</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001141</t>
+          <t>ARI:0001140</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ARI:0001151</t>
+          <t>ARI:0001150</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
